--- a/output/roomself_excel/20060.xlsx
+++ b/output/roomself_excel/20060.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>362659</v>
+        <v>127985</v>
       </c>
       <c r="D2" t="n">
-        <v>6844</v>
+        <v>3096</v>
       </c>
       <c r="E2" t="n">
-        <v>1031</v>
+        <v>545</v>
       </c>
       <c r="F2" t="n">
-        <v>456</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>102080</v>
+        <v>169806</v>
       </c>
       <c r="D3" t="n">
-        <v>2688</v>
+        <v>3440</v>
       </c>
       <c r="E3" t="n">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="F3" t="n">
-        <v>263</v>
+        <v>455</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31832</v>
+        <v>54054</v>
       </c>
       <c r="D4" t="n">
-        <v>1428</v>
+        <v>1860</v>
       </c>
       <c r="E4" t="n">
-        <v>184</v>
+        <v>268</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>54054</v>
+        <v>64868</v>
       </c>
       <c r="D5" t="n">
-        <v>1860</v>
+        <v>2304</v>
       </c>
       <c r="E5" t="n">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -568,6 +568,50 @@
       </c>
       <c r="F6" t="n">
         <v>34</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>102080</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2688</v>
+      </c>
+      <c r="E7" t="n">
+        <v>475</v>
+      </c>
+      <c r="F7" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>31832</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1428</v>
+      </c>
+      <c r="E8" t="n">
+        <v>184</v>
+      </c>
+      <c r="F8" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/20060.xlsx
+++ b/output/roomself_excel/20060.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,62 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
         </is>
       </c>
     </row>
@@ -475,12 +525,34 @@
       <c r="D2" t="n">
         <v>3096</v>
       </c>
-      <c r="E2" t="n">
-        <v>545</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>279</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>246</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +569,49 @@
       <c r="D3" t="n">
         <v>3440</v>
       </c>
-      <c r="E3" t="n">
-        <v>486</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>455</v>
+        <v>150</v>
+      </c>
+      <c r="G3" t="n">
+        <v>35</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J3" t="n">
+        <v>48</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>102</v>
+      </c>
+      <c r="M3" t="n">
+        <v>30</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>375</v>
+      </c>
+      <c r="P3" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +629,34 @@
       <c r="D4" t="n">
         <v>1860</v>
       </c>
-      <c r="E4" t="n">
-        <v>268</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>262</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="G4" t="n">
+        <v>31</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>231</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +673,18 @@
       <c r="D5" t="n">
         <v>2304</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +701,26 @@
       <c r="D6" t="n">
         <v>1088</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>148</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>34</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +737,34 @@
       <c r="D7" t="n">
         <v>2688</v>
       </c>
-      <c r="E7" t="n">
-        <v>475</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>263</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="G7" t="n">
+        <v>35</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>440</v>
+      </c>
+      <c r="J7" t="n">
+        <v>31</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +781,26 @@
       <c r="D8" t="n">
         <v>1428</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>184</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>31</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
